--- a/rules/CORE-000842/negative/02/data/unit-test-coreid-CG0213-negative 2.xlsx
+++ b/rules/CORE-000842/negative/02/data/unit-test-coreid-CG0213-negative 2.xlsx
@@ -37,7 +37,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -63,18 +63,13 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <i/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -82,12 +77,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125">
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFCC"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -129,7 +118,7 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -138,7 +127,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -532,7 +520,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F10"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="str">
@@ -555,19 +543,19 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="4" t="str">
         <v>sv.xpt</v>
       </c>
-      <c r="C2" s="2" t="str">
+      <c r="C2" s="4" t="str">
         <v>Record</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="4">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="str">
+      <c r="E2" s="4" t="str">
         <v>SVUPDES</v>
       </c>
     </row>
@@ -593,7 +581,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4" s="2" t="str">
         <v>sv.xpt</v>
@@ -602,10 +590,13 @@
         <v>Record</v>
       </c>
       <c r="D4" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E4" s="2" t="str">
-        <v>SVUPDES</v>
+        <v>VISIT</v>
+      </c>
+      <c r="F4" s="2" t="str">
+        <v>WEEK 4: UNSCHEDULED 01</v>
       </c>
     </row>
     <row r="5">
@@ -622,52 +613,109 @@
         <v>13</v>
       </c>
       <c r="E5" s="4" t="str">
+        <v>SVUPDES</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4">
+        <v>2</v>
+      </c>
+      <c r="B6" s="4" t="str">
+        <v>sv.xpt</v>
+      </c>
+      <c r="C6" s="4" t="str">
+        <v>Record</v>
+      </c>
+      <c r="D6" s="4">
+        <v>13</v>
+      </c>
+      <c r="E6" s="4" t="str">
         <v>VISITNUM</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F6" s="4">
         <v>101</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2">
+    <row r="7">
+      <c r="A7" s="2">
+        <v>2</v>
+      </c>
+      <c r="B7" s="2" t="str">
+        <v>sv.xpt</v>
+      </c>
+      <c r="C7" s="2" t="str">
+        <v>Record</v>
+      </c>
+      <c r="D7" s="2">
+        <v>13</v>
+      </c>
+      <c r="E7" s="2" t="str">
+        <v>VISIT</v>
+      </c>
+      <c r="F7" s="2" t="str">
+        <v>EARLY DISCONTINUATION</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4">
         <v>3</v>
       </c>
-      <c r="B6" s="2" t="str">
+      <c r="B8" s="4" t="str">
         <v>sv.xpt</v>
       </c>
-      <c r="C6" s="2" t="str">
+      <c r="C8" s="4" t="str">
         <v>Record</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D8" s="4">
         <v>14</v>
       </c>
-      <c r="E6" s="2" t="str">
+      <c r="E8" s="4" t="str">
         <v>SVUPDES</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4">
+    <row r="9">
+      <c r="A9" s="4">
         <v>3</v>
       </c>
-      <c r="B7" s="4" t="str">
+      <c r="B9" s="4" t="str">
         <v>sv.xpt</v>
       </c>
-      <c r="C7" s="4" t="str">
+      <c r="C9" s="4" t="str">
         <v>Record</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D9" s="4">
         <v>14</v>
       </c>
-      <c r="E7" s="4" t="str">
+      <c r="E9" s="4" t="str">
         <v>VISITNUM</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F9" s="4">
         <v>201</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2">
+        <v>3</v>
+      </c>
+      <c r="B10" s="2" t="str">
+        <v>sv.xpt</v>
+      </c>
+      <c r="C10" s="2" t="str">
+        <v>Record</v>
+      </c>
+      <c r="D10" s="2">
+        <v>14</v>
+      </c>
+      <c r="E10" s="2" t="str">
+        <v>VISIT</v>
+      </c>
+      <c r="F10" s="2" t="str">
+        <v>EARLY DISCONTINUATION RETRIEVAL</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F10"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -715,104 +763,104 @@
       <c r="A2" s="5" t="str">
         <v>Study Identifier</v>
       </c>
-      <c r="B2" s="6" t="str">
+      <c r="B2" s="5" t="str">
         <v>Domain Abbreviation</v>
       </c>
-      <c r="C2" s="6" t="str">
+      <c r="C2" s="5" t="str">
         <v>Unique Subject Identifier</v>
       </c>
-      <c r="D2" s="6" t="str">
+      <c r="D2" s="5" t="str">
         <v>Visit Number</v>
       </c>
-      <c r="E2" s="6" t="str">
+      <c r="E2" s="5" t="str">
         <v>Visit Name</v>
       </c>
-      <c r="F2" s="6" t="str">
+      <c r="F2" s="5" t="str">
         <v>Pre-specified</v>
       </c>
-      <c r="G2" s="6" t="str">
+      <c r="G2" s="5" t="str">
         <v>Visit Day</v>
       </c>
-      <c r="H2" s="6" t="str">
+      <c r="H2" s="5" t="str">
         <v>Start Date/Time of Visit</v>
       </c>
-      <c r="I2" s="6" t="str">
+      <c r="I2" s="5" t="str">
         <v>End Date/Time of Visit</v>
       </c>
-      <c r="J2" s="6" t="str">
+      <c r="J2" s="5" t="str">
         <v>Study Day of Start of Visit</v>
       </c>
-      <c r="K2" s="6" t="str">
+      <c r="K2" s="5" t="str">
         <v>Study Day of End of Visit</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="str">
+      <c r="A3" s="5" t="str">
         <v>Char</v>
       </c>
-      <c r="B3" s="6" t="str">
+      <c r="B3" s="5" t="str">
         <v>Char</v>
       </c>
-      <c r="C3" s="6" t="str">
+      <c r="C3" s="5" t="str">
         <v>Char</v>
       </c>
-      <c r="D3" s="6" t="str">
+      <c r="D3" s="5" t="str">
         <v>Num</v>
       </c>
-      <c r="E3" s="6" t="str">
+      <c r="E3" s="5" t="str">
         <v>Char</v>
       </c>
-      <c r="F3" s="6" t="str">
+      <c r="F3" s="5" t="str">
         <v>Char</v>
       </c>
-      <c r="G3" s="6" t="str">
+      <c r="G3" s="5" t="str">
         <v>Num</v>
       </c>
-      <c r="H3" s="6" t="str">
+      <c r="H3" s="5" t="str">
         <v>Char</v>
       </c>
-      <c r="I3" s="6" t="str">
+      <c r="I3" s="5" t="str">
         <v>Char</v>
       </c>
-      <c r="J3" s="6" t="str">
+      <c r="J3" s="5" t="str">
         <v>Num</v>
       </c>
-      <c r="K3" s="6" t="str">
+      <c r="K3" s="5" t="str">
         <v>Num</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6">
+      <c r="A4" s="5">
         <v>12</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>2</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>8</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <v>8</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="5">
         <v>200</v>
       </c>
-      <c r="F4" s="6" t="str">
+      <c r="F4" s="5" t="str">
         <v>2</v>
       </c>
-      <c r="G4" s="6" t="str">
+      <c r="G4" s="5" t="str">
         <v>8</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="5">
         <v>10</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="5">
         <v>10</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="5">
         <v>8</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="5">
         <v>8</v>
       </c>
     </row>
@@ -1001,10 +1049,10 @@
       <c r="C10" s="4" t="str">
         <v>CDISC001</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="6">
         <v>5.01</v>
       </c>
-      <c r="E10" s="4" t="str">
+      <c r="E10" s="7" t="str">
         <v>WEEK 4: UNSCHEDULED 01</v>
       </c>
       <c r="F10" s="4" t="str">
@@ -1106,10 +1154,10 @@
       <c r="C13" s="4" t="str">
         <v>CDISC001</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="6">
         <v>101</v>
       </c>
-      <c r="E13" s="4" t="str">
+      <c r="E13" s="7" t="str">
         <v>EARLY DISCONTINUATION</v>
       </c>
       <c r="F13" s="4" t="str">
@@ -1141,10 +1189,10 @@
       <c r="C14" s="4" t="str">
         <v>CDISC001</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="6">
         <v>201</v>
       </c>
-      <c r="E14" s="4" t="str">
+      <c r="E14" s="7" t="str">
         <v>EARLY DISCONTINUATION RETRIEVAL</v>
       </c>
       <c r="F14" s="4" t="str">
@@ -1201,71 +1249,71 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="str">
+      <c r="A2" s="5" t="str">
         <v>Study Identifier</v>
       </c>
-      <c r="B2" s="6" t="str">
+      <c r="B2" s="5" t="str">
         <v>Domain Abbreviation</v>
       </c>
-      <c r="C2" s="6" t="str">
+      <c r="C2" s="5" t="str">
         <v>Visit Number</v>
       </c>
-      <c r="D2" s="6" t="str">
+      <c r="D2" s="5" t="str">
         <v>Visit Name</v>
       </c>
-      <c r="E2" s="6" t="str">
+      <c r="E2" s="5" t="str">
         <v>Planned Arm Code</v>
       </c>
-      <c r="F2" s="6" t="str">
+      <c r="F2" s="5" t="str">
         <v>Visit Start Rule</v>
       </c>
-      <c r="G2" s="6" t="str">
+      <c r="G2" s="5" t="str">
         <v>Visit End Rule</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="str">
+      <c r="A3" s="5" t="str">
         <v>Char</v>
       </c>
-      <c r="B3" s="6" t="str">
+      <c r="B3" s="5" t="str">
         <v>Char</v>
       </c>
-      <c r="C3" s="6" t="str">
+      <c r="C3" s="5" t="str">
         <v>Num</v>
       </c>
-      <c r="D3" s="6" t="str">
+      <c r="D3" s="5" t="str">
         <v>Char</v>
       </c>
-      <c r="E3" s="6" t="str">
+      <c r="E3" s="5" t="str">
         <v>Char</v>
       </c>
-      <c r="F3" s="6" t="str">
+      <c r="F3" s="5" t="str">
         <v>Char</v>
       </c>
-      <c r="G3" s="6" t="str">
+      <c r="G3" s="5" t="str">
         <v>Char</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6">
+      <c r="A4" s="5">
         <v>12</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>2</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>8</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <v>200</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="5">
         <v>8</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="5">
         <v>200</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="5">
         <v>200</v>
       </c>
     </row>
